--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_hoog.xlsx
@@ -406,7 +406,7 @@
         <v>1506</v>
       </c>
       <c r="C2">
-        <v>1483</v>
+        <v>1541</v>
       </c>
       <c r="D2">
         <v>1054</v>
@@ -418,7 +418,7 @@
         <v>1540</v>
       </c>
       <c r="G2">
-        <v>1589</v>
+        <v>1605</v>
       </c>
       <c r="H2">
         <v>1643</v>
@@ -432,7 +432,7 @@
         <v>1544</v>
       </c>
       <c r="C3">
-        <v>1490</v>
+        <v>1552</v>
       </c>
       <c r="D3">
         <v>1029</v>
@@ -444,7 +444,7 @@
         <v>1565</v>
       </c>
       <c r="G3">
-        <v>1594</v>
+        <v>1610</v>
       </c>
       <c r="H3">
         <v>1651</v>
@@ -458,7 +458,7 @@
         <v>1422</v>
       </c>
       <c r="C4">
-        <v>1537</v>
+        <v>1542</v>
       </c>
       <c r="D4">
         <v>770</v>
@@ -470,7 +470,7 @@
         <v>1458</v>
       </c>
       <c r="G4">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="H4">
         <v>1630</v>
@@ -484,7 +484,7 @@
         <v>1600</v>
       </c>
       <c r="C5">
-        <v>1589</v>
+        <v>1609</v>
       </c>
       <c r="D5">
         <v>373</v>
@@ -496,7 +496,7 @@
         <v>1601</v>
       </c>
       <c r="G5">
-        <v>1604</v>
+        <v>1621</v>
       </c>
       <c r="H5">
         <v>1666</v>
@@ -510,7 +510,7 @@
         <v>1585</v>
       </c>
       <c r="C6">
-        <v>1586</v>
+        <v>1603</v>
       </c>
       <c r="D6">
         <v>188</v>
@@ -522,7 +522,7 @@
         <v>1588</v>
       </c>
       <c r="G6">
-        <v>1592</v>
+        <v>1609</v>
       </c>
       <c r="H6">
         <v>1663</v>
@@ -536,19 +536,19 @@
         <v>1612</v>
       </c>
       <c r="C7">
-        <v>1595</v>
+        <v>1620</v>
       </c>
       <c r="D7">
         <v>341</v>
       </c>
       <c r="E7">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="F7">
         <v>1614</v>
       </c>
       <c r="G7">
-        <v>1606</v>
+        <v>1630</v>
       </c>
       <c r="H7">
         <v>1667</v>
@@ -562,22 +562,22 @@
         <v>1524</v>
       </c>
       <c r="C8">
-        <v>1433</v>
+        <v>1494</v>
       </c>
       <c r="D8">
         <v>326</v>
       </c>
       <c r="E8">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="F8">
         <v>1525</v>
       </c>
       <c r="G8">
-        <v>1466</v>
+        <v>1515</v>
       </c>
       <c r="H8">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -588,7 +588,7 @@
         <v>1625</v>
       </c>
       <c r="C9">
-        <v>1547</v>
+        <v>1575</v>
       </c>
       <c r="D9">
         <v>428</v>
@@ -600,7 +600,7 @@
         <v>1628</v>
       </c>
       <c r="G9">
-        <v>1566</v>
+        <v>1594</v>
       </c>
       <c r="H9">
         <v>1663</v>
@@ -614,7 +614,7 @@
         <v>1570</v>
       </c>
       <c r="C10">
-        <v>1590</v>
+        <v>1612</v>
       </c>
       <c r="D10">
         <v>1009</v>
@@ -626,7 +626,7 @@
         <v>1596</v>
       </c>
       <c r="G10">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="H10">
         <v>1664</v>
@@ -640,7 +640,7 @@
         <v>1555</v>
       </c>
       <c r="C11">
-        <v>1592</v>
+        <v>1620</v>
       </c>
       <c r="D11">
         <v>917</v>
@@ -652,7 +652,7 @@
         <v>1581</v>
       </c>
       <c r="G11">
-        <v>1637</v>
+        <v>1645</v>
       </c>
       <c r="H11">
         <v>1665</v>
@@ -666,7 +666,7 @@
         <v>1298</v>
       </c>
       <c r="C12">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="D12">
         <v>477</v>
@@ -678,7 +678,7 @@
         <v>1344</v>
       </c>
       <c r="G12">
-        <v>1606</v>
+        <v>1614</v>
       </c>
       <c r="H12">
         <v>1650</v>
@@ -692,7 +692,7 @@
         <v>1560</v>
       </c>
       <c r="C13">
-        <v>1588</v>
+        <v>1608</v>
       </c>
       <c r="D13">
         <v>881</v>
@@ -704,7 +704,7 @@
         <v>1584</v>
       </c>
       <c r="G13">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="H13">
         <v>1662</v>
